--- a/data/evaluation/instances/instance_evaluation_2.xlsx
+++ b/data/evaluation/instances/instance_evaluation_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mathieu/Documents/Work/PhD Years/PhD/Code/XWSRP/inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mathieu/Documents/Work/PhD Years/PhD/Code/XWSRP/data/evaluation/instances/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F396C9-37C2-E64A-BABD-C30240510105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECD95BC-3BF9-7546-A25E-FB8D65D6C1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="16620" activeTab="2" xr2:uid="{745759C5-7123-8144-B92E-2C75C62BB0A9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="150">
   <si>
     <t>Latitude</t>
   </si>
@@ -460,6 +460,33 @@
   </si>
   <si>
     <t>14.4246659</t>
+  </si>
+  <si>
+    <t>T33</t>
+  </si>
+  <si>
+    <t>47.35158</t>
+  </si>
+  <si>
+    <t>14.99612</t>
+  </si>
+  <si>
+    <t>T34</t>
+  </si>
+  <si>
+    <t>47.70636</t>
+  </si>
+  <si>
+    <t>14.50759</t>
+  </si>
+  <si>
+    <t>T35</t>
+  </si>
+  <si>
+    <t>48.120326</t>
+  </si>
+  <si>
+    <t>15.804151</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA72F52-AB34-1E4A-8B1D-E76BD6529E91}">
-  <dimension ref="A1:N120"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
@@ -1044,7 +1071,7 @@
     <col min="8" max="8" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -1070,7 +1097,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1096,7 +1123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1122,7 +1149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1148,7 +1175,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1174,7 +1201,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1200,7 +1227,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1226,7 +1253,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1252,7 +1279,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1278,7 +1305,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1303,23 +1330,8 @@
       <c r="H10" t="s">
         <v>128</v>
       </c>
-      <c r="J10">
-        <v>40</v>
-      </c>
-      <c r="K10" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10" t="s">
-        <v>127</v>
-      </c>
-      <c r="N10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1345,7 +1357,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1371,7 +1383,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1397,7 +1409,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1423,7 +1435,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1449,7 +1461,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1918,13 +1930,82 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D34" s="1"/>
+      <c r="A34" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" s="1">
+        <v>25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D35" s="1"/>
+      <c r="A35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" s="1">
+        <v>60</v>
+      </c>
+      <c r="E35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D36" s="1"/>
+      <c r="A36" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" s="1">
+        <v>30</v>
+      </c>
+      <c r="E36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D37" s="1"/>
